--- a/exports/internships_2026-08-12.xlsx
+++ b/exports/internships_2026-08-12.xlsx
@@ -7,9 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internships" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Open" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="New Today" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Open'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'New Today'!$A$1:$K$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,18 +31,43 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF7E6"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -53,10 +82,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,249 +457,373 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Fit Score</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Posted Date</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Age (days)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Fit Reason</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Apply Link</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Internship/Master Thesis (f/m/x) - Multimodal LLM Assistant for Traffic Safety - Forschung, Ingenieur</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>English Jobs</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>custom:English Jobs</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Role cue: «Internship/Master Thesis (f/m/» · Domain: «r Thesis (f/m/x) - Multimodal LLM Assistant for Traffic Safety» · Keyword: «f/m/x) - Multimodal LLM Assistant for Traff» · embedding sim=0.52</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Role: «Internship/Master Thesis (f/m/» · Domain: «sis (f/m/x) - Multimodal LLM Assistant for Traffic Sa» · [role=25 domain=20 recency=4 language=4]</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>https://englishjobs.de/clickout/b9fae1ce3a43957b?ql=l&amp;sig=0276316118a8811bb503abe31fd7bf2d8975117f&amp;e=e6_uiP5XhFY4A9GoKt7FsKt_6NdM4JsKm8yiWuOJB3BWrHmnQlffcRLnl1Wzl2_gbo9f6ywHThKhw-g7PH8sXWy1tWtiXEClnvzcQSGEuf5pNXlXF6UKz6LszGtpBzUC4sPF9viee0O9YrsWvmw2BEH9LZ0i0Q0LBtzn1Ni68nn8Hbqtak8nCR05RS0RWrC0-WqWmKyAaWBrKpR9PeGd_0n4YhdgMQUMzmtSp_AzFsViCx5ANnYjQme4cYKzY4tvMTmiFsZzumD2HulpDiSPdLsZWJzS1lbzO_TZYCPceA2kUdZtIqPydW347qyNF1hDLt88aQK2TN22YHt5yYr_Pt5ySXEkS4yJegVU8mPQWZduCxzQ71rqqHfIe_FrfrCqaoiD5GMh3s5hvl1-qlEs8l5BpHTUzuirY9yHRSSALAQBoX4wmxxmOay88RU-aw-4dRfbn_EkgMe3TXK6ftcq-cchRsIQuaiinM_HcCrHwWgAKp-JsYPAstL3mIkPXywTeVNG3ozAoNpGt0HEA2Vdwi6CmMP1xoiYe-2p4nSYLqps8cC6Bdjt66wfw2AJM8EiXUOm5_c9fzqFsln-4GsO7r7Mhhqq43Ld4xlP9L66BvSaFVjOP1DSk6YuSz9bbqxaSWhzAnXBaiMDRkEdbgLlBkDZINA69blR7VgVtXeJOj9sp1EsRGCx8bGeaMb67-V87gagMr4iHYaInbOSevfD98YSnxIKm0dnJUSgCEjJnssZpmeBqwb5AwMyoobKyVsGt7M-SrcQV3HnvSXqvy46veVEF5D4tW_nNTEYb0n3bxVNMUwGWS3jCcSq_dLjzj7vZHY1RLXkZ4XK3ZZzOmWCiAcl36GxJhN0VZrA-YeM49xLkB4AImGAaBSgePpLicciU7ykE80H7k4DKcO1TutJFB1hY3lvifLo807teAgfLuO-ZOYm-FyMtlIMMDOp71HepSUDsgmC-JZhRWuvsfU4tg0C8e-k_LkB-ai895okivXyya8mVp5CEeM48ynAD_nvBwzFPPQ3gfXZY3WYST_lZonxxkGtk7wXrROh-yEWXy9UAgv6fUPB3pAmTkWXhErOo6UgkvRGdwyLjuF8JP1YfbDWpr1GvQuEEbdQaMZFSSRBY9Q3Wpb8n8YPyJN2jJDa1NxhuH1ujE3bRbp97E67VeCxS0l4qu33LQcon1idAPZu_-bKZgedEIsvIisxommUm2pWHip1K2LLrv2L2o-9GaQd3xhkrhZ3-Flk431R7mfuOoc63UAp-z1J81sk_Yf9WfvhP2Ady_IUZyBdotgT_W8zUiCkVfOv8MJz1-TSke0-PLYQk_aLQproVrr4bg2Vs6iRithXh35pDgIIt8DT4gNl1f6VMcrTPsGqwVi3ylX7vkKLLqAQYCNtwmTF0ulqvJrD-omvRY-IujvYm16qkX11iGUrIIlFMbxr_V1DPz-BlZlo9FFFHI1Bp1FR8OiyiCqmXvsnBlXP-5X_tWnsIjtGhJuTfJEXigKue9cLY0lLWs1remzZ0pyrj_XC-ISEfiYyX1Ld7DBOw48_vEzOkzM4MeurlUKzz7Sk-q0t-oFvpx2ANI1L3AuV4_iBD2d2ZNWU1yL_i-VewnAD1BoLcX4sxxYtITm5W2BWUCk8nkldOo54YLtW8q1Qs7nBGpW1MFFgTebqoOELzwlUNOZ17ADIZon1t9-vd_DhsK0UbgqUNPCEVyGXUCR38rBw_eEYVVt082kaPgdG5FgWgnHuE5AQdcOqjKs2eLKB9KRpUH2WHLCzw2IlUqK1W24xsE9vX3QJDF4WM9wYkeNGoXWXIie5lwdH2MFcWRqDVc8KK6SI5EwAMCoCi4_CyiAiPysSZEAdjw5190U240nHrxB_-VvMIq8fPYxk1qt-kbL_5cYH3dcVg4J1gbxNf4M3LTZp4AYFdQX1K9qkd3D6La2_JpSO0Vuzgy08caulHqz58P6t_hkdFkP6BDRm5D-UpaYLwuwxHpSGEA&amp;prev=RQ2E85C9BF67C307&amp;p=5&amp;pg=1</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>User Acquisition Intern</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ALMEDIA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Werkstudent*in Digital Factory Campus Berlin für Digitale Produktionsprozesse</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Group</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Berlin, BE, DE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>jobspy:indeed</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Role cue: «his is a full\-time internship, not a working stud» · English working language detected in posting · Keyword: «nywhere else. We’re aiming to become Germa» · embedding sim=0.34</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>https://de.indeed.com/viewjob?jk=cfb0ea6383495c79</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>E-commerce Intern</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Savage X</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Berlin, BE, DE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>jobspy:indeed</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Role cue: «*   Throughout your internship, you'll gain practi» · English: «tten and verbal communication skills in English. * Strong analytical mindset with an in» · Keyword: «d CRM to deliver seamless customer experie» · embedding sim=0.31</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>https://de.indeed.com/viewjob?jk=1010f8d5513208af</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Werkstudent*in Digital Factory Campus Berlin für Digitale Produktionsprozesse</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz Group</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Berlin, BE, DE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>jobspy:indeed</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Role cue: «Werkstudent*in Digital Factory» · Domain: «chaftsinformatik, Informatik, Data Science, Maschinenbau, Mathematik ode» · Keyword: «ise mit Confluence, Python oder Web\-Technolog» · embedding sim=0.33</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Role: «Werkstudent*in Digital Factory» · Domain: «sinformatik, Informatik, Data Science, Maschinenbau, Mathemati» · [role=25 domain=9 language=1]</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>https://de.indeed.com/viewjob?jk=e95c21c99bf2372a</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fit Score</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Age (days)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fit Reason</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Apply Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Internship/Master Thesis (f/m/x) - Multimodal LLM Assistant for Traffic Safety - Forschung, Ingenieur</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>English Jobs</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>custom:English Jobs</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Role: «Internship/Master Thesis (f/m/» · Domain: «sis (f/m/x) - Multimodal LLM Assistant for Traffic Sa» · [role=25 domain=20 recency=4 language=4]</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>https://englishjobs.de/clickout/b9fae1ce3a43957b?ql=l&amp;sig=0276316118a8811bb503abe31fd7bf2d8975117f&amp;e=e6_uiP5XhFY4A9GoKt7FsKt_6NdM4JsKm8yiWuOJB3BWrHmnQlffcRLnl1Wzl2_gbo9f6ywHThKhw-g7PH8sXWy1tWtiXEClnvzcQSGEuf5pNXlXF6UKz6LszGtpBzUC4sPF9viee0O9YrsWvmw2BEH9LZ0i0Q0LBtzn1Ni68nn8Hbqtak8nCR05RS0RWrC0-WqWmKyAaWBrKpR9PeGd_0n4YhdgMQUMzmtSp_AzFsViCx5ANnYjQme4cYKzY4tvMTmiFsZzumD2HulpDiSPdLsZWJzS1lbzO_TZYCPceA2kUdZtIqPydW347qyNF1hDLt88aQK2TN22YHt5yYr_Pt5ySXEkS4yJegVU8mPQWZduCxzQ71rqqHfIe_FrfrCqaoiD5GMh3s5hvl1-qlEs8l5BpHTUzuirY9yHRSSALAQBoX4wmxxmOay88RU-aw-4dRfbn_EkgMe3TXK6ftcq-cchRsIQuaiinM_HcCrHwWgAKp-JsYPAstL3mIkPXywTeVNG3ozAoNpGt0HEA2Vdwi6CmMP1xoiYe-2p4nSYLqps8cC6Bdjt66wfw2AJM8EiXUOm5_c9fzqFsln-4GsO7r7Mhhqq43Ld4xlP9L66BvSaFVjOP1DSk6YuSz9bbqxaSWhzAnXBaiMDRkEdbgLlBkDZINA69blR7VgVtXeJOj9sp1EsRGCx8bGeaMb67-V87gagMr4iHYaInbOSevfD98YSnxIKm0dnJUSgCEjJnssZpmeBqwb5AwMyoobKyVsGt7M-SrcQV3HnvSXqvy46veVEF5D4tW_nNTEYb0n3bxVNMUwGWS3jCcSq_dLjzj7vZHY1RLXkZ4XK3ZZzOmWCiAcl36GxJhN0VZrA-YeM49xLkB4AImGAaBSgePpLicciU7ykE80H7k4DKcO1TutJFB1hY3lvifLo807teAgfLuO-ZOYm-FyMtlIMMDOp71HepSUDsgmC-JZhRWuvsfU4tg0C8e-k_LkB-ai895okivXyya8mVp5CEeM48ynAD_nvBwzFPPQ3gfXZY3WYST_lZonxxkGtk7wXrROh-yEWXy9UAgv6fUPB3pAmTkWXhErOo6UgkvRGdwyLjuF8JP1YfbDWpr1GvQuEEbdQaMZFSSRBY9Q3Wpb8n8YPyJN2jJDa1NxhuH1ujE3bRbp97E67VeCxS0l4qu33LQcon1idAPZu_-bKZgedEIsvIisxommUm2pWHip1K2LLrv2L2o-9GaQd3xhkrhZ3-Flk431R7mfuOoc63UAp-z1J81sk_Yf9WfvhP2Ady_IUZyBdotgT_W8zUiCkVfOv8MJz1-TSke0-PLYQk_aLQproVrr4bg2Vs6iRithXh35pDgIIt8DT4gNl1f6VMcrTPsGqwVi3ylX7vkKLLqAQYCNtwmTF0ulqvJrD-omvRY-IujvYm16qkX11iGUrIIlFMbxr_V1DPz-BlZlo9FFFHI1Bp1FR8OiyiCqmXvsnBlXP-5X_tWnsIjtGhJuTfJEXigKue9cLY0lLWs1remzZ0pyrj_XC-ISEfiYyX1Ld7DBOw48_vEzOkzM4MeurlUKzz7Sk-q0t-oFvpx2ANI1L3AuV4_iBD2d2ZNWU1yL_i-VewnAD1BoLcX4sxxYtITm5W2BWUCk8nkldOo54YLtW8q1Qs7nBGpW1MFFgTebqoOELzwlUNOZ17ADIZon1t9-vd_DhsK0UbgqUNPCEVyGXUCR38rBw_eEYVVt082kaPgdG5FgWgnHuE5AQdcOqjKs2eLKB9KRpUH2WHLCzw2IlUqK1W24xsE9vX3QJDF4WM9wYkeNGoXWXIie5lwdH2MFcWRqDVc8KK6SI5EwAMCoCi4_CyiAiPysSZEAdjw5190U240nHrxB_-VvMIq8fPYxk1qt-kbL_5cYH3dcVg4J1gbxNf4M3LTZp4AYFdQX1K9qkd3D6La2_JpSO0Vuzgy08caulHqz58P6t_hkdFkP6BDRm5D-UpaYLwuwxHpSGEA&amp;prev=RQ2E85C9BF67C307&amp;p=5&amp;pg=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Werkstudent*in Digital Factory Campus Berlin für Digitale Produktionsprozesse</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Group</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Berlin, BE, DE</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>jobspy:indeed</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Role: «Werkstudent*in Digital Factory» · Domain: «sinformatik, Informatik, Data Science, Maschinenbau, Mathemati» · [role=25 domain=9 language=1]</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>https://de.indeed.com/viewjob?jk=e95c21c99bf2372a</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K3"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
